--- a/diseases/d127/2000-2004.xlsx
+++ b/diseases/d127/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2347,9 +2335,6 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">

--- a/diseases/d127/2000-2004.xlsx
+++ b/diseases/d127/2000-2004.xlsx
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -2385,42 +2385,42 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2498,22 +2498,22 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_PL_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Other Viral Haemorrhagic fevers</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:PL:national</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
@@ -2619,42 +2619,828 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
           <t>is_doh_annual</t>
         </is>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2774,7 +3560,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2784,7 +3570,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -2804,7 +3590,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2814,7 +3600,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d127/2000-2004.xlsx
+++ b/diseases/d127/2000-2004.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -765,24 +765,99 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -790,25 +865,30 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -910,12 +990,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -1015,7 +1095,7 @@
         </is>
       </c>
       <c r="AN3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1024,25 +1104,30 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1114,12 +1199,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1144,12 +1229,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1168,7 +1253,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1193,7 +1278,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1206,42 +1291,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1358,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1303,12 +1388,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1319,22 +1404,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Viral Haemorrhagic Fever</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1344,7 +1429,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1359,7 +1444,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1384,7 +1469,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1394,12 +1479,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1427,7 +1512,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1440,42 +1525,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1587,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1551,24 +1636,99 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1576,25 +1736,30 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1661,17 +1826,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1696,12 +1861,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1710,34 +1875,17 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Blæðandi veiruhitasóttir</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1745,64 +1893,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1820,7 +1910,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1833,42 +1923,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1895,17 +1985,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1944,17 +2034,34 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1962,6 +2069,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1979,7 +2144,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1992,42 +2157,42 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2359,7 @@
         </is>
       </c>
       <c r="AN9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -2203,25 +2368,30 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2686,12 +2856,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2740,7 +2910,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2765,7 +2935,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT12" t="n">
@@ -2778,42 +2948,42 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2845,12 +3015,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2891,22 +3061,22 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Blæðandi veiruhitasóttir</t>
+          <t>Viral Haemorrhagic Fever</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2916,7 +3086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2931,7 +3101,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2956,7 +3126,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2966,12 +3136,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2999,7 +3169,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT13" t="n">
@@ -3012,42 +3182,42 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3074,17 +3244,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3123,17 +3293,34 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_VIRAL_HEMORRHAGIC_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Blæðandi veiruhitasóttir</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -3141,6 +3328,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>0</v>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3148,65 +3393,70 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3483,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3282,98 +3532,23 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Other Viral Haemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>country:PL:national</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN15" t="b">
-        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -3439,6 +3614,240 @@
         </is>
       </c>
       <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Other Viral Haemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -3560,7 +3969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -3570,7 +3979,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3590,7 +3999,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -3600,7 +4009,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
